--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488146_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488146_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5781</v>
+        <v>5.7974</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6095</v>
+        <v>6.0012</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0314</v>
+        <v>-0.2038</v>
       </c>
       <c r="G2" t="n">
         <v>3.8132</v>
@@ -610,13 +610,13 @@
         <v>2.4087</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.764</v>
+        <v>-0.5447</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6056</v>
+        <v>-0.2139</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1585</v>
+        <v>-0.3308</v>
       </c>
       <c r="V2" t="n">
         <v>3.0848</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0341</v>
+        <v>2.4203</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9145</v>
+        <v>2.6207</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1196</v>
+        <v>-0.2004</v>
       </c>
       <c r="G3" t="n">
         <v>2.3721</v>
@@ -688,13 +688,13 @@
         <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2179</v>
+        <v>0.604</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7039</v>
+        <v>0.4101</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5141</v>
+        <v>0.194</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. MERINO LUQUE</t>
+          <t>A. ELIAS GALLEGOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3097</v>
+        <v>1.1765</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8704</v>
+        <v>0.374</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4393</v>
+        <v>0.8025</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1614</v>
+        <v>-0.2117</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9372</v>
+        <v>1.2291</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2242</v>
+        <v>-1.4408</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1835</v>
+        <v>-0.2209</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7428</v>
+        <v>1.0434</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5592</v>
+        <v>-1.2643</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9779</v>
+        <v>0.0092</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1944</v>
+        <v>0.1857</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7834</v>
+        <v>-0.1766</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.4823</v>
+        <v>0.7411</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0006</v>
+        <v>0.3326</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4661</v>
+        <v>0.2804</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5345</v>
+        <v>0.0522</v>
       </c>
       <c r="V4" t="n">
-        <v>0.63</v>
+        <v>0.3144</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ELIAS GALLEGOS</t>
+          <t>R. SANAHUJA TRESERRAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9118</v>
+        <v>1.0094</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9616</v>
+        <v>2.5385</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9503</v>
+        <v>-1.5291</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2117</v>
+        <v>3.2002</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2291</v>
+        <v>0.4249</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4408</v>
+        <v>2.7753</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2209</v>
+        <v>4.4384</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0434</v>
+        <v>1.2024</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2643</v>
+        <v>3.236</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0092</v>
+        <v>-1.2382</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1857</v>
+        <v>-0.7775</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1766</v>
+        <v>-0.4607</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7411</v>
+        <v>1.6676</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0679</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.868</v>
+        <v>-0.1582</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1999</v>
+        <v>-0.6367</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3144</v>
+        <v>-1.9517</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3144</v>
+        <v>-0.63</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.3217</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. SANAHUJA TRESERRAS</t>
+          <t>R. MERINO LUQUE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2659</v>
+        <v>0.9616</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6571</v>
+        <v>-0.2068</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9231</v>
+        <v>1.1685</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2002</v>
+        <v>1.1614</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4249</v>
+        <v>0.9372</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7753</v>
+        <v>0.2242</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4384</v>
+        <v>0.1835</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2024</v>
+        <v>0.7428</v>
       </c>
       <c r="L6" t="n">
-        <v>3.236</v>
+        <v>-0.5592</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2382</v>
+        <v>0.9779</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7775</v>
+        <v>0.1944</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4607</v>
+        <v>0.7834</v>
       </c>
       <c r="P6" t="n">
+        <v>-1.4823</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-2.0382</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.5558999999999999</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-1.1117</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.6676</v>
-      </c>
       <c r="S6" t="n">
-        <v>-2.0702</v>
+        <v>0.6525</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0396</v>
+        <v>0.3889</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0307</v>
+        <v>0.2636</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.9517</v>
+        <v>0.63</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.63</v>
+        <v>1.2589</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3217</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3335</v>
+        <v>-0.0386</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4052</v>
+        <v>-2.3073</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0717</v>
+        <v>2.2687</v>
       </c>
       <c r="G7" t="n">
         <v>0.3746</v>
@@ -1000,13 +1000,13 @@
         <v>1.297</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.534</v>
+        <v>-0.2391</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1057</v>
+        <v>0.2036</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6397</v>
+        <v>-0.4427</v>
       </c>
       <c r="V7" t="n">
         <v>0.5671</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2712</v>
+        <v>-0.9528</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7741</v>
+        <v>-0.4803</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4972</v>
+        <v>-0.4725</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3088</v>
@@ -1078,13 +1078,13 @@
         <v>0.1853</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1477</v>
+        <v>0.1707</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1641</v>
+        <v>0.1296</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4986</v>
+        <v>-3.2837</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6021</v>
+        <v>1.1124</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.1007</v>
+        <v>-4.3961</v>
       </c>
       <c r="G9" t="n">
         <v>-0.212</v>
@@ -1156,13 +1156,13 @@
         <v>1.4823</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3502</v>
+        <v>-0.4349</v>
       </c>
       <c r="T9" t="n">
-        <v>0.485</v>
+        <v>-0.0046</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1348</v>
+        <v>-0.4303</v>
       </c>
       <c r="V9" t="n">
         <v>-2.2662</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2797</v>
+        <v>-4.7151</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3863</v>
+        <v>-0.0925</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.8934</v>
+        <v>-4.6226</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9307</v>
@@ -1234,13 +1234,13 @@
         <v>0.9264</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1289</v>
+        <v>-0.5643</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6566</v>
+        <v>-0.3628</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4723</v>
+        <v>-0.2015</v>
       </c>
       <c r="V10" t="n">
         <v>-3.1466</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7891</v>
+        <v>-4.9794</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2145</v>
+        <v>-2.7249</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5746</v>
+        <v>-2.2545</v>
       </c>
       <c r="G11" t="n">
         <v>-3.9939</v>
@@ -1312,13 +1312,13 @@
         <v>1.297</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5089</v>
+        <v>-0.6992</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8207</v>
+        <v>-0.3311</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6882</v>
+        <v>-0.3681</v>
       </c>
       <c r="V11" t="n">
         <v>1.196</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.604299999999999</v>
+        <v>-2.604399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>6.835099999999998</v>
+        <v>6.835000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.439499999999999</v>
+        <v>-9.439299999999999</v>
       </c>
       <c r="G12" t="n">
         <v>3.2644</v>
@@ -1369,7 +1369,7 @@
         <v>12.3312</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.8049000000000004</v>
       </c>
       <c r="M12" t="n">
         <v>-9.8718</v>
@@ -1378,7 +1378,7 @@
         <v>-1.8856</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.9865</v>
+        <v>-7.986499999999999</v>
       </c>
       <c r="P12" t="n">
         <v>-2.779399999999999</v>
@@ -1390,16 +1390,16 @@
         <v>12.0436</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.517099999999999</v>
+        <v>-1.5173</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3420999999999998</v>
+        <v>0.342</v>
       </c>
       <c r="U12" t="n">
         <v>-1.8593</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.572199999999999</v>
+        <v>-1.5722</v>
       </c>
       <c r="W12" t="n">
         <v>8.1798</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.7157</v>
+        <v>2.2053</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7304</v>
+        <v>1.22</v>
       </c>
       <c r="F13" t="n">
         <v>0.9853</v>
@@ -1468,10 +1468,10 @@
         <v>1.4823</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5223</v>
+        <v>-0.0326</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8207</v>
+        <v>-0.3311</v>
       </c>
       <c r="U13" t="n">
         <v>0.2984</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6581</v>
+        <v>2.1976</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7629</v>
+        <v>4.1546</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.1048</v>
+        <v>-1.957</v>
       </c>
       <c r="G14" t="n">
         <v>3.945</v>
@@ -1546,13 +1546,13 @@
         <v>1.297</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9162</v>
+        <v>-0.3768</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1131</v>
+        <v>0.2786</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8031</v>
+        <v>-0.6554</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6294</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. ÁLVAREZ RICO</t>
+          <t>A. GONZALEZ PALOMO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5662</v>
+        <v>1.8062</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5662</v>
+        <v>2.0528</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0.2466</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5662</v>
+        <v>0.2832</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3221</v>
+        <v>0.4614</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2441</v>
+        <v>-0.1782</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5662</v>
+        <v>1.2023</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3221</v>
+        <v>1.1809</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2441</v>
+        <v>0.0214</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-0.9191</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-0.7196</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0.1996</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.3939</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>0.2036</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.1903</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LATORRE SANCHEZ</t>
+          <t>A. ÁLVAREZ RICO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5555</v>
+        <v>1.5662</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0178</v>
+        <v>1.5662</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4623</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7103</v>
+        <v>1.5662</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1758</v>
+        <v>0.3221</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8861</v>
+        <v>1.2441</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8185</v>
+        <v>1.5662</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3055</v>
+        <v>0.3221</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.487</v>
+        <v>1.2441</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5288</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.1297</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3991</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4087</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.594</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1164</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7000999999999999</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4163</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2594</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PALOMO</t>
+          <t>J. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4374</v>
+        <v>1.0888</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9549</v>
+        <v>1.822</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5174</v>
+        <v>-0.7332</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2832</v>
+        <v>-0.7103</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4614</v>
+        <v>0.1758</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1782</v>
+        <v>-0.8861</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2023</v>
+        <v>1.8185</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1809</v>
+        <v>2.3055</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0214</v>
+        <v>-0.487</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9191</v>
+        <v>-2.5288</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7196</v>
+        <v>-2.1297</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1996</v>
+        <v>-0.3991</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1853</v>
+        <v>2.4087</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>-0.1853</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1117</v>
+        <v>2.594</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0251</v>
+        <v>0.6498</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1057</v>
+        <v>0.5043</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0806</v>
+        <v>0.1455</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9439</v>
+        <v>-1.2594</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5733</v>
+        <v>-0.3155</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6294</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>Á. GONZÁLEZ PALOMO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2007</v>
+        <v>0.3221</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1896</v>
+        <v>0.3221</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0111</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1644</v>
+        <v>0.3221</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2982</v>
+        <v>0.3221</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1338</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8279</v>
+        <v>0.3221</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.3221</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2488</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9922</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8773</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.115</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2353</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9737</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2616</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9444</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Á. GONZÁLEZ PALOMO</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3221</v>
+        <v>0.2454</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3221</v>
+        <v>0.3082</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3221</v>
+        <v>-1.1644</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3221</v>
+        <v>-1.2982</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.1338</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3221</v>
+        <v>0.8279</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3221</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.2488</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-1.9922</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-1.8773</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.115</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.2801</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.0924</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.1878</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.9444</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. VIDAL</t>
+          <t>R. FREIRE DELTIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1768</v>
+        <v>0.1005</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0831</v>
+        <v>-0.2982</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2599</v>
+        <v>0.3987</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3333</v>
+        <v>-0.8439</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.3288</v>
+        <v>-0.5368000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0045</v>
+        <v>-0.3071</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4837</v>
+        <v>-0.5455</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.5251</v>
+        <v>-0.5455</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0415</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8497</v>
+        <v>-0.2984</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8037</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.046</v>
+        <v>-0.3071</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9264</v>
+        <v>0.3706</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1117</v>
+        <v>-0.1853</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0382</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8601</v>
+        <v>-0.3706</v>
       </c>
       <c r="T20" t="n">
-        <v>1.7907</v>
+        <v>0.1181</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0694</v>
+        <v>-0.4887</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.63</v>
+        <v>0.9444</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8877</v>
+        <v>0.3144</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.5177</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. FREIRE DELTIO</t>
+          <t>A. FERNANDEZ AMESTOY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3897</v>
+        <v>-0.2004</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6899</v>
+        <v>-0.317</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3002</v>
+        <v>0.1166</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8439</v>
+        <v>-0.5198</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.9714</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3071</v>
+        <v>0.4517</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5455</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5455</v>
+        <v>-0.5884</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.0829</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2984</v>
+        <v>-0.0143</v>
       </c>
       <c r="N21" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.383</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3071</v>
+        <v>0.3687</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3706</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1853</v>
+        <v>-0.9264</v>
       </c>
       <c r="R21" t="n">
         <v>0.5558999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8608</v>
+        <v>0.06</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2736</v>
+        <v>-0.1439</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.2039</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9444</v>
+        <v>0.63</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3144</v>
+        <v>1.2589</v>
       </c>
       <c r="X21" t="n">
-        <v>0.63</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ AMESTOY</t>
+          <t>H. ANDRADE CORREIA E SILVA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4449</v>
+        <v>-0.4017</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6108</v>
+        <v>1.7328</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1659</v>
+        <v>-2.1345</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5198</v>
+        <v>1.0707</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9714</v>
+        <v>-0.0552</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4517</v>
+        <v>1.1259</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5054999999999999</v>
+        <v>3.2547</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5884</v>
+        <v>1.9063</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0829</v>
+        <v>1.3484</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0143</v>
+        <v>-2.184</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.383</v>
+        <v>-1.9614</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3687</v>
+        <v>-0.2226</v>
       </c>
       <c r="P22" t="n">
         <v>-0.3706</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9264</v>
+        <v>-2.0382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.6676</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1845</v>
+        <v>0.157</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4377</v>
+        <v>0.2018</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2532</v>
+        <v>-0.0448</v>
       </c>
       <c r="V22" t="n">
-        <v>0.63</v>
+        <v>-1.2589</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6289</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H. ANDRADE CORREIA E SILVA</t>
+          <t>B. VIDAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4297</v>
+        <v>-1.3038</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6555</v>
+        <v>0.1038</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0852</v>
+        <v>-1.4076</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0707</v>
+        <v>-2.3333</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0552</v>
+        <v>-2.3288</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1259</v>
+        <v>-0.0045</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2547</v>
+        <v>-1.4837</v>
       </c>
       <c r="K23" t="n">
-        <v>1.9063</v>
+        <v>-1.5251</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3484</v>
+        <v>0.0415</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.184</v>
+        <v>-0.8497</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.9614</v>
+        <v>-0.8037</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2226</v>
+        <v>-0.046</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0382</v>
+        <v>-1.1117</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6676</v>
+        <v>2.0382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.871</v>
+        <v>0.7331</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8754</v>
+        <v>0.8114</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0045</v>
+        <v>-0.0784</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2589</v>
+        <v>-0.63</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3144</v>
+        <v>1.8877</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5733</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5483</v>
+        <v>-1.597</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0441</v>
+        <v>-2.142</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4958</v>
+        <v>0.5451</v>
       </c>
       <c r="G24" t="n">
         <v>-0.6758</v>
@@ -2326,13 +2326,13 @@
         <v>1.1117</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1313</v>
+        <v>-0.18</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0584</v>
+        <v>-0.1564</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0236</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.862</v>
+        <v>-3.425</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4982</v>
+        <v>-1.0858</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3638</v>
+        <v>-2.3392</v>
       </c>
       <c r="G25" t="n">
         <v>-4.6457</v>
@@ -2404,13 +2404,13 @@
         <v>1.297</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7663</v>
+        <v>0.2033</v>
       </c>
       <c r="T25" t="n">
-        <v>0.868</v>
+        <v>0.2804</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1017</v>
+        <v>-0.0771</v>
       </c>
       <c r="V25" t="n">
         <v>1.5733</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2.604299999999999</v>
+        <v>2.6042</v>
       </c>
       <c r="E26" t="n">
-        <v>9.439500000000001</v>
+        <v>9.439499999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.835099999999999</v>
+        <v>-6.8352</v>
       </c>
       <c r="G26" t="n">
         <v>-3.2642</v>
@@ -2458,7 +2458,7 @@
         <v>9.871799999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>1.8857</v>
+        <v>1.885699999999999</v>
       </c>
       <c r="L26" t="n">
         <v>7.986300000000002</v>
@@ -2473,7 +2473,7 @@
         <v>-0.8048999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>2.779300000000001</v>
+        <v>2.7793</v>
       </c>
       <c r="Q26" t="n">
         <v>-12.0437</v>
@@ -2482,10 +2482,10 @@
         <v>14.823</v>
       </c>
       <c r="S26" t="n">
-        <v>1.5171</v>
+        <v>1.5172</v>
       </c>
       <c r="T26" t="n">
-        <v>1.8593</v>
+        <v>1.8592</v>
       </c>
       <c r="U26" t="n">
         <v>-0.3421000000000001</v>
